--- a/Deliverables/BOM/LCD_Board_1.0.3/eSpark_BOM_LCD_Board_1.0.3.xlsx
+++ b/Deliverables/BOM/LCD_Board_1.0.3/eSpark_BOM_LCD_Board_1.0.3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Oliver-ARC\Deliverables\BOM\LCD_Board_1.0.3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED4D438C-1783-449C-804D-C2DEB4EA40B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43D69F61-C16A-4F9E-87FB-A81D8D07F196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -777,6 +777,27 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -808,27 +829,6 @@
     <xf numFmtId="0" fontId="20" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="15" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="15" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1206,15 +1206,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="60"/>
-      <c r="L1" s="60"/>
-      <c r="M1" s="60"/>
-      <c r="N1" s="60"/>
-      <c r="O1" s="60"/>
-      <c r="P1" s="60"/>
-      <c r="Q1" s="60"/>
-      <c r="R1" s="60"/>
-      <c r="S1" s="61"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
+      <c r="N1" s="67"/>
+      <c r="O1" s="67"/>
+      <c r="P1" s="67"/>
+      <c r="Q1" s="67"/>
+      <c r="R1" s="67"/>
+      <c r="S1" s="68"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1264,7 +1264,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="62"/>
+      <c r="S3" s="69"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1289,7 +1289,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="63"/>
+      <c r="S4" s="70"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1314,7 +1314,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="63"/>
+      <c r="S5" s="70"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1335,7 +1335,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="63"/>
+      <c r="S6" s="70"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -1356,7 +1356,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="63"/>
+      <c r="S7" s="70"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -1377,7 +1377,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="63"/>
+      <c r="S8" s="70"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -1442,7 +1442,7 @@
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="73" t="s">
+      <c r="C10" s="63" t="s">
         <v>33</v>
       </c>
       <c r="D10" s="46" t="s">
@@ -1479,7 +1479,7 @@
       <c r="N10" s="46">
         <v>6</v>
       </c>
-      <c r="O10" s="75" t="s">
+      <c r="O10" s="65" t="s">
         <v>37</v>
       </c>
       <c r="P10" s="54">
@@ -1498,7 +1498,7 @@
         <f t="shared" ref="B11" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="74" t="s">
+      <c r="C11" s="64" t="s">
         <v>33</v>
       </c>
       <c r="D11" s="50" t="s">
@@ -1528,14 +1528,14 @@
       <c r="L11" s="51">
         <v>1</v>
       </c>
-      <c r="M11" s="72">
+      <c r="M11" s="62">
         <f>L11*5</f>
         <v>5</v>
       </c>
       <c r="N11" s="50">
         <v>10</v>
       </c>
-      <c r="O11" s="76" t="s">
+      <c r="O11" s="66" t="s">
         <v>37</v>
       </c>
       <c r="P11" s="55">
@@ -1562,17 +1562,17 @@
       <c r="K12" s="37"/>
       <c r="L12" s="37"/>
       <c r="M12" s="37"/>
-      <c r="N12" s="68" t="s">
+      <c r="N12" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="O12" s="69"/>
-      <c r="P12" s="69"/>
-      <c r="Q12" s="70">
+      <c r="O12" s="76"/>
+      <c r="P12" s="76"/>
+      <c r="Q12" s="60">
         <f>SUM(Q10:Q11)</f>
         <v>2.2984</v>
       </c>
-      <c r="R12" s="64"/>
-      <c r="S12" s="65"/>
+      <c r="R12" s="71"/>
+      <c r="S12" s="72"/>
     </row>
     <row r="13" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
@@ -1588,17 +1588,17 @@
       <c r="K13" s="10"/>
       <c r="L13" s="10"/>
       <c r="M13" s="10"/>
-      <c r="N13" s="68" t="s">
+      <c r="N13" s="75" t="s">
         <v>31</v>
       </c>
-      <c r="O13" s="69"/>
-      <c r="P13" s="69"/>
-      <c r="Q13" s="71">
+      <c r="O13" s="76"/>
+      <c r="P13" s="76"/>
+      <c r="Q13" s="61">
         <f>Q12/5</f>
         <v>0.45967999999999998</v>
       </c>
-      <c r="R13" s="66"/>
-      <c r="S13" s="67"/>
+      <c r="R13" s="73"/>
+      <c r="S13" s="74"/>
     </row>
   </sheetData>
   <mergeCells count="5">
